--- a/03_bloques/B01/B01_trabajo.xlsx
+++ b/03_bloques/B01/B01_trabajo.xlsx
@@ -638,7 +638,7 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -932,7 +932,7 @@
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       <c r="G34" s="3" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2638,7 +2638,7 @@
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2685,7 +2685,7 @@
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2983,7 +2983,7 @@
       <c r="G50" s="3" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       <c r="G53" s="3" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       <c r="G56" s="3" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       <c r="G62" s="3" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3881,7 +3881,7 @@
       <c r="G68" s="3" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -4081,7 +4081,7 @@
       <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -4128,7 +4128,7 @@
       <c r="G73" s="3" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       <c r="G77" s="3" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -4426,7 +4426,7 @@
       <c r="G79" s="5" t="inlineStr"/>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4575,7 +4575,7 @@
       <c r="G82" s="3" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4724,7 +4724,7 @@
       <c r="G85" s="5" t="inlineStr"/>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -4873,7 +4873,7 @@
       <c r="G88" s="3" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       <c r="G91" s="5" t="inlineStr"/>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -5171,7 +5171,7 @@
       <c r="G94" s="3" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -5320,7 +5320,7 @@
       <c r="G97" s="5" t="inlineStr"/>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -5418,7 +5418,7 @@
       <c r="G99" s="3" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       <c r="G103" s="3" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       <c r="G107" s="5" t="inlineStr"/>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
@@ -5865,7 +5865,7 @@
       <c r="G108" s="3" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       <c r="G113" s="5" t="inlineStr"/>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
@@ -6163,7 +6163,7 @@
       <c r="G114" s="3" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -6414,7 +6414,7 @@
       <c r="G119" s="5" t="inlineStr"/>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
@@ -6461,7 +6461,7 @@
       <c r="G120" s="3" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       <c r="G123" s="3" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       <c r="G125" s="5" t="inlineStr"/>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
@@ -6908,7 +6908,7 @@
       <c r="G129" s="3" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       <c r="G131" s="5" t="inlineStr"/>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
@@ -7155,7 +7155,7 @@
       <c r="G134" s="3" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
@@ -7304,7 +7304,7 @@
       <c r="G137" s="5" t="inlineStr"/>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
@@ -7453,7 +7453,7 @@
       <c r="G140" s="3" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr">
@@ -7602,7 +7602,7 @@
       <c r="G143" s="5" t="inlineStr"/>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
@@ -7751,7 +7751,7 @@
       <c r="G146" s="3" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
@@ -7951,7 +7951,7 @@
       <c r="G150" s="3" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
@@ -8100,7 +8100,7 @@
       <c r="G153" s="3" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
@@ -8300,7 +8300,7 @@
       <c r="G157" s="3" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
@@ -8551,7 +8551,7 @@
       <c r="G162" s="5" t="inlineStr"/>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I162" s="4" t="inlineStr">
@@ -8598,7 +8598,7 @@
       <c r="G163" s="3" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
@@ -8849,7 +8849,7 @@
       <c r="G168" s="3" t="inlineStr"/>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
@@ -8998,7 +8998,7 @@
       <c r="G171" s="3" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
@@ -9096,7 +9096,7 @@
       <c r="G173" s="5" t="inlineStr"/>
       <c r="H173" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
@@ -9143,7 +9143,7 @@
       <c r="G174" s="5" t="inlineStr"/>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I174" s="4" t="inlineStr">
@@ -9343,7 +9343,7 @@
       <c r="G178" s="3" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
@@ -9390,7 +9390,7 @@
       <c r="G179" s="5" t="inlineStr"/>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
@@ -9437,7 +9437,7 @@
       <c r="G180" s="5" t="inlineStr"/>
       <c r="H180" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I180" s="4" t="inlineStr">
@@ -9586,7 +9586,7 @@
       <c r="G183" s="3" t="inlineStr"/>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       <c r="G186" s="5" t="inlineStr"/>
       <c r="H186" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I186" s="4" t="inlineStr">
@@ -9884,7 +9884,7 @@
       <c r="G189" s="3" t="inlineStr"/>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
@@ -10029,7 +10029,7 @@
       <c r="G192" s="5" t="inlineStr"/>
       <c r="H192" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I192" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       <c r="G195" s="3" t="inlineStr"/>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -10276,7 +10276,7 @@
       <c r="G197" s="5" t="inlineStr"/>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I197" s="4" t="inlineStr">
@@ -10323,7 +10323,7 @@
       <c r="G198" s="5" t="inlineStr"/>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I198" s="4" t="inlineStr">
@@ -10421,7 +10421,7 @@
       <c r="G200" s="3" t="inlineStr"/>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
   <autoFilter ref="A1:K201"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Borrador,Sin borrador,Revisar_Juan,Enviado,Validado,Grabado"</formula1>
+      <formula1>"Borrador,Sin borrador,Por_revisar,Enviado,Validado,Grabado"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -26364,7 +26364,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Español redactado o adaptado por Claude (Revisar_Juan)</t>
+          <t>Español redactado o adaptado por Claude (Por_revisar)</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
